--- a/data/macro/Europe/Interest Rate.xlsx
+++ b/data/macro/Europe/Interest Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\Europe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959B713A-287F-4F27-AE48-0726E183DC20}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8ABA74-B5B0-4105-B914-E689285CBA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EUAPRRT" sheetId="1" r:id="rId1"/>
@@ -71,8 +71,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -136,24 +136,24 @@
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -444,14 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G284"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G285"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="2" customWidth="1"/>
-    <col min="5" max="7" width="9.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -486,7 +486,7 @@
         <v>36161</v>
       </c>
       <c r="C2" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E2" s="12">
         <v>0.03</v>
@@ -500,7 +500,7 @@
         <v>36192</v>
       </c>
       <c r="C3" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E3" s="12">
         <v>0.03</v>
@@ -517,7 +517,7 @@
         <v>36220</v>
       </c>
       <c r="C4" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E4" s="12">
         <v>0.03</v>
@@ -534,7 +534,7 @@
         <v>36251</v>
       </c>
       <c r="C5" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E5" s="12">
         <v>0.03</v>
@@ -551,7 +551,7 @@
         <v>36281</v>
       </c>
       <c r="C6" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E6" s="12">
         <v>2.5000000000000001E-2</v>
@@ -568,7 +568,7 @@
         <v>36312</v>
       </c>
       <c r="C7" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E7" s="12">
         <v>2.5000000000000001E-2</v>
@@ -585,7 +585,7 @@
         <v>36342</v>
       </c>
       <c r="C8" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E8" s="12">
         <v>2.5000000000000001E-2</v>
@@ -602,7 +602,7 @@
         <v>36373</v>
       </c>
       <c r="C9" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E9" s="12">
         <v>2.5000000000000001E-2</v>
@@ -619,7 +619,7 @@
         <v>36404</v>
       </c>
       <c r="C10" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E10" s="12">
         <v>2.5000000000000001E-2</v>
@@ -636,7 +636,7 @@
         <v>36434</v>
       </c>
       <c r="C11" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E11" s="12">
         <v>2.5000000000000001E-2</v>
@@ -653,7 +653,7 @@
         <v>36465</v>
       </c>
       <c r="C12" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E12" s="12">
         <v>2.5000000000000001E-2</v>
@@ -670,7 +670,7 @@
         <v>36495</v>
       </c>
       <c r="C13" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E13" s="12">
         <v>0.03</v>
@@ -687,7 +687,7 @@
         <v>36526</v>
       </c>
       <c r="C14" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E14" s="12">
         <v>0.03</v>
@@ -704,7 +704,7 @@
         <v>36557</v>
       </c>
       <c r="C15" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E15" s="12">
         <v>0.03</v>
@@ -721,7 +721,7 @@
         <v>36586</v>
       </c>
       <c r="C16" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E16" s="12">
         <v>3.2500000000000001E-2</v>
@@ -738,7 +738,7 @@
         <v>36617</v>
       </c>
       <c r="C17" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E17" s="12">
         <v>3.5000000000000003E-2</v>
@@ -755,7 +755,7 @@
         <v>36647</v>
       </c>
       <c r="C18" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E18" s="12">
         <v>3.7499999999999999E-2</v>
@@ -772,7 +772,7 @@
         <v>36678</v>
       </c>
       <c r="C19" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E19" s="12">
         <v>3.7499999999999999E-2</v>
@@ -789,7 +789,7 @@
         <v>36708</v>
       </c>
       <c r="C20" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E20" s="12">
         <v>4.2500000000000003E-2</v>
@@ -806,7 +806,7 @@
         <v>36739</v>
       </c>
       <c r="C21" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E21" s="12">
         <v>4.2500000000000003E-2</v>
@@ -823,7 +823,7 @@
         <v>36770</v>
       </c>
       <c r="C22" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E22" s="12">
         <v>4.4999999999999998E-2</v>
@@ -840,7 +840,7 @@
         <v>36800</v>
       </c>
       <c r="C23" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E23" s="12">
         <v>4.4999999999999998E-2</v>
@@ -857,7 +857,7 @@
         <v>36831</v>
       </c>
       <c r="C24" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E24" s="12">
         <v>4.7500000000000001E-2</v>
@@ -874,7 +874,7 @@
         <v>36861</v>
       </c>
       <c r="C25" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E25" s="12">
         <v>4.7500000000000001E-2</v>
@@ -891,7 +891,7 @@
         <v>36892</v>
       </c>
       <c r="C26" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E26" s="12">
         <v>4.7500000000000001E-2</v>
@@ -908,7 +908,7 @@
         <v>36923</v>
       </c>
       <c r="C27" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E27" s="12">
         <v>4.7500000000000001E-2</v>
@@ -925,7 +925,7 @@
         <v>36951</v>
       </c>
       <c r="C28" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E28" s="12">
         <v>4.7500000000000001E-2</v>
@@ -942,7 +942,7 @@
         <v>36982</v>
       </c>
       <c r="C29" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E29" s="12">
         <v>4.7500000000000001E-2</v>
@@ -959,7 +959,7 @@
         <v>37012</v>
       </c>
       <c r="C30" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E30" s="12">
         <v>4.7500000000000001E-2</v>
@@ -976,7 +976,7 @@
         <v>37043</v>
       </c>
       <c r="C31" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E31" s="12">
         <v>4.4999999999999998E-2</v>
@@ -993,7 +993,7 @@
         <v>37073</v>
       </c>
       <c r="C32" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E32" s="12">
         <v>4.4999999999999998E-2</v>
@@ -1010,7 +1010,7 @@
         <v>37104</v>
       </c>
       <c r="C33" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E33" s="12">
         <v>4.4999999999999998E-2</v>
@@ -1027,7 +1027,7 @@
         <v>37135</v>
       </c>
       <c r="C34" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E34" s="12">
         <v>4.2500000000000003E-2</v>
@@ -1044,7 +1044,7 @@
         <v>37165</v>
       </c>
       <c r="C35" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E35" s="12">
         <v>3.7499999999999999E-2</v>
@@ -1061,7 +1061,7 @@
         <v>37196</v>
       </c>
       <c r="C36" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E36" s="12">
         <v>3.7499999999999999E-2</v>
@@ -1078,7 +1078,7 @@
         <v>37226</v>
       </c>
       <c r="C37" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E37" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1095,7 +1095,7 @@
         <v>37257</v>
       </c>
       <c r="C38" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E38" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1112,7 +1112,7 @@
         <v>37288</v>
       </c>
       <c r="C39" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E39" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1129,7 +1129,7 @@
         <v>37316</v>
       </c>
       <c r="C40" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E40" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1146,7 +1146,7 @@
         <v>37347</v>
       </c>
       <c r="C41" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E41" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1163,7 +1163,7 @@
         <v>37377</v>
       </c>
       <c r="C42" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E42" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1180,7 +1180,7 @@
         <v>37408</v>
       </c>
       <c r="C43" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E43" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1197,7 +1197,7 @@
         <v>37438</v>
       </c>
       <c r="C44" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E44" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1214,7 +1214,7 @@
         <v>37469</v>
       </c>
       <c r="C45" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E45" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1231,7 +1231,7 @@
         <v>37500</v>
       </c>
       <c r="C46" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E46" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1248,7 +1248,7 @@
         <v>37530</v>
       </c>
       <c r="C47" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E47" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1265,7 +1265,7 @@
         <v>37561</v>
       </c>
       <c r="C48" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E48" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1282,7 +1282,7 @@
         <v>37591</v>
       </c>
       <c r="C49" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E49" s="12">
         <v>3.2500000000000001E-2</v>
@@ -1299,7 +1299,7 @@
         <v>37622</v>
       </c>
       <c r="C50" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E50" s="12">
         <v>2.75E-2</v>
@@ -1316,7 +1316,7 @@
         <v>37653</v>
       </c>
       <c r="C51" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E51" s="12">
         <v>2.75E-2</v>
@@ -1333,7 +1333,7 @@
         <v>37681</v>
       </c>
       <c r="C52" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E52" s="12">
         <v>2.75E-2</v>
@@ -1350,7 +1350,7 @@
         <v>37712</v>
       </c>
       <c r="C53" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E53" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1367,7 +1367,7 @@
         <v>37742</v>
       </c>
       <c r="C54" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E54" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1384,7 +1384,7 @@
         <v>37773</v>
       </c>
       <c r="C55" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E55" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1401,7 +1401,7 @@
         <v>37803</v>
       </c>
       <c r="C56" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E56" s="12">
         <v>0.02</v>
@@ -1418,7 +1418,7 @@
         <v>37834</v>
       </c>
       <c r="C57" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E57" s="12">
         <v>0.02</v>
@@ -1435,7 +1435,7 @@
         <v>37865</v>
       </c>
       <c r="C58" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E58" s="12">
         <v>0.02</v>
@@ -1452,7 +1452,7 @@
         <v>37895</v>
       </c>
       <c r="C59" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E59" s="12">
         <v>0.02</v>
@@ -1469,7 +1469,7 @@
         <v>37926</v>
       </c>
       <c r="C60" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E60" s="12">
         <v>0.02</v>
@@ -1486,7 +1486,7 @@
         <v>37956</v>
       </c>
       <c r="C61" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E61" s="12">
         <v>0.02</v>
@@ -1503,7 +1503,7 @@
         <v>37987</v>
       </c>
       <c r="C62" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E62" s="12">
         <v>0.02</v>
@@ -1520,7 +1520,7 @@
         <v>38018</v>
       </c>
       <c r="C63" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E63" s="12">
         <v>0.02</v>
@@ -1537,7 +1537,7 @@
         <v>38047</v>
       </c>
       <c r="C64" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E64" s="12">
         <v>0.02</v>
@@ -1554,7 +1554,7 @@
         <v>38078</v>
       </c>
       <c r="C65" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E65" s="12">
         <v>0.02</v>
@@ -1571,7 +1571,7 @@
         <v>38108</v>
       </c>
       <c r="C66" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E66" s="12">
         <v>0.02</v>
@@ -1588,7 +1588,7 @@
         <v>38139</v>
       </c>
       <c r="C67" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E67" s="12">
         <v>0.02</v>
@@ -1605,7 +1605,7 @@
         <v>38169</v>
       </c>
       <c r="C68" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E68" s="12">
         <v>0.02</v>
@@ -1622,7 +1622,7 @@
         <v>38200</v>
       </c>
       <c r="C69" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E69" s="12">
         <v>0.02</v>
@@ -1639,7 +1639,7 @@
         <v>38231</v>
       </c>
       <c r="C70" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E70" s="12">
         <v>0.02</v>
@@ -1656,7 +1656,7 @@
         <v>38261</v>
       </c>
       <c r="C71" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E71" s="12">
         <v>0.02</v>
@@ -1673,7 +1673,7 @@
         <v>38292</v>
       </c>
       <c r="C72" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E72" s="12">
         <v>0.02</v>
@@ -1690,7 +1690,7 @@
         <v>38322</v>
       </c>
       <c r="C73" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E73" s="12">
         <v>0.02</v>
@@ -1707,7 +1707,7 @@
         <v>38353</v>
       </c>
       <c r="C74" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E74" s="12">
         <v>0.02</v>
@@ -1724,7 +1724,7 @@
         <v>38384</v>
       </c>
       <c r="C75" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E75" s="12">
         <v>0.02</v>
@@ -1741,7 +1741,7 @@
         <v>38412</v>
       </c>
       <c r="C76" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E76" s="12">
         <v>0.02</v>
@@ -1758,7 +1758,7 @@
         <v>38443</v>
       </c>
       <c r="C77" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E77" s="12">
         <v>0.02</v>
@@ -1775,7 +1775,7 @@
         <v>38473</v>
       </c>
       <c r="C78" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E78" s="12">
         <v>0.02</v>
@@ -1792,7 +1792,7 @@
         <v>38504</v>
       </c>
       <c r="C79" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E79" s="12">
         <v>0.02</v>
@@ -1809,7 +1809,7 @@
         <v>38534</v>
       </c>
       <c r="C80" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E80" s="12">
         <v>0.02</v>
@@ -1826,7 +1826,7 @@
         <v>38565</v>
       </c>
       <c r="C81" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E81" s="12">
         <v>0.02</v>
@@ -1843,7 +1843,7 @@
         <v>38596</v>
       </c>
       <c r="C82" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E82" s="12">
         <v>0.02</v>
@@ -1860,7 +1860,7 @@
         <v>38626</v>
       </c>
       <c r="C83" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E83" s="12">
         <v>0.02</v>
@@ -1877,7 +1877,7 @@
         <v>38657</v>
       </c>
       <c r="C84" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E84" s="12">
         <v>0.02</v>
@@ -1894,7 +1894,7 @@
         <v>38687</v>
       </c>
       <c r="C85" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E85" s="12">
         <v>0.02</v>
@@ -1911,7 +1911,7 @@
         <v>38718</v>
       </c>
       <c r="C86" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E86" s="12">
         <v>2.2499999999999999E-2</v>
@@ -1928,7 +1928,7 @@
         <v>38749</v>
       </c>
       <c r="C87" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E87" s="12">
         <v>2.2499999999999999E-2</v>
@@ -1945,7 +1945,7 @@
         <v>38777</v>
       </c>
       <c r="C88" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E88" s="12">
         <v>2.2499999999999999E-2</v>
@@ -1962,7 +1962,7 @@
         <v>38808</v>
       </c>
       <c r="C89" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E89" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1979,7 +1979,7 @@
         <v>38838</v>
       </c>
       <c r="C90" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E90" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1996,7 +1996,7 @@
         <v>38869</v>
       </c>
       <c r="C91" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E91" s="12">
         <v>2.5000000000000001E-2</v>
@@ -2013,7 +2013,7 @@
         <v>38899</v>
       </c>
       <c r="C92" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E92" s="12">
         <v>2.75E-2</v>
@@ -2030,7 +2030,7 @@
         <v>38930</v>
       </c>
       <c r="C93" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E93" s="12">
         <v>2.75E-2</v>
@@ -2047,7 +2047,7 @@
         <v>38961</v>
       </c>
       <c r="C94" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E94" s="12">
         <v>0.03</v>
@@ -2064,7 +2064,7 @@
         <v>38991</v>
       </c>
       <c r="C95" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E95" s="12">
         <v>0.03</v>
@@ -2081,7 +2081,7 @@
         <v>39022</v>
       </c>
       <c r="C96" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E96" s="12">
         <v>3.2500000000000001E-2</v>
@@ -2098,7 +2098,7 @@
         <v>39052</v>
       </c>
       <c r="C97" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E97" s="12">
         <v>3.2500000000000001E-2</v>
@@ -2115,7 +2115,7 @@
         <v>39083</v>
       </c>
       <c r="C98" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E98" s="12">
         <v>3.5000000000000003E-2</v>
@@ -2132,7 +2132,7 @@
         <v>39114</v>
       </c>
       <c r="C99" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E99" s="12">
         <v>3.5000000000000003E-2</v>
@@ -2149,7 +2149,7 @@
         <v>39142</v>
       </c>
       <c r="C100" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E100" s="12">
         <v>3.5000000000000003E-2</v>
@@ -2166,7 +2166,7 @@
         <v>39173</v>
       </c>
       <c r="C101" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E101" s="12">
         <v>3.7499999999999999E-2</v>
@@ -2183,7 +2183,7 @@
         <v>39203</v>
       </c>
       <c r="C102" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E102" s="12">
         <v>3.7499999999999999E-2</v>
@@ -2200,7 +2200,7 @@
         <v>39234</v>
       </c>
       <c r="C103" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E103" s="12">
         <v>3.7499999999999999E-2</v>
@@ -2217,7 +2217,7 @@
         <v>39264</v>
       </c>
       <c r="C104" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E104" s="12">
         <v>0.04</v>
@@ -2234,7 +2234,7 @@
         <v>39295</v>
       </c>
       <c r="C105" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E105" s="12">
         <v>0.04</v>
@@ -2251,7 +2251,7 @@
         <v>39326</v>
       </c>
       <c r="C106" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E106" s="12">
         <v>0.04</v>
@@ -2268,7 +2268,7 @@
         <v>39356</v>
       </c>
       <c r="C107" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E107" s="12">
         <v>0.04</v>
@@ -2285,7 +2285,7 @@
         <v>39387</v>
       </c>
       <c r="C108" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E108" s="12">
         <v>0.04</v>
@@ -2302,7 +2302,7 @@
         <v>39417</v>
       </c>
       <c r="C109" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E109" s="12">
         <v>0.04</v>
@@ -2319,7 +2319,7 @@
         <v>39448</v>
       </c>
       <c r="C110" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E110" s="12">
         <v>0.04</v>
@@ -2336,7 +2336,7 @@
         <v>39479</v>
       </c>
       <c r="C111" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.34375</v>
       </c>
       <c r="E111" s="12">
         <v>0.04</v>
@@ -2353,7 +2353,7 @@
         <v>39513</v>
       </c>
       <c r="C112" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E112" s="12">
         <v>0.04</v>
@@ -2373,7 +2373,7 @@
         <v>39548</v>
       </c>
       <c r="C113" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E113" s="12">
         <v>0.04</v>
@@ -2393,7 +2393,7 @@
         <v>39576</v>
       </c>
       <c r="C114" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E114" s="12">
         <v>0.04</v>
@@ -2413,7 +2413,7 @@
         <v>39604</v>
       </c>
       <c r="C115" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E115" s="12">
         <v>0.04</v>
@@ -2433,7 +2433,7 @@
         <v>39632</v>
       </c>
       <c r="C116" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E116" s="12">
         <v>4.2500000000000003E-2</v>
@@ -2453,7 +2453,7 @@
         <v>39667</v>
       </c>
       <c r="C117" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E117" s="12">
         <v>4.2500000000000003E-2</v>
@@ -2473,7 +2473,7 @@
         <v>39695</v>
       </c>
       <c r="C118" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E118" s="12">
         <v>4.2500000000000003E-2</v>
@@ -2493,7 +2493,7 @@
         <v>39723</v>
       </c>
       <c r="C119" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E119" s="12">
         <v>4.2500000000000003E-2</v>
@@ -2513,7 +2513,7 @@
         <v>39729</v>
       </c>
       <c r="C120" s="9">
-        <v>0.25</v>
+        <v>0.34375</v>
       </c>
       <c r="E120" s="12">
         <v>3.7499999999999999E-2</v>
@@ -2530,7 +2530,7 @@
         <v>39758</v>
       </c>
       <c r="C121" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E121" s="12">
         <v>3.2500000000000001E-2</v>
@@ -2550,7 +2550,7 @@
         <v>39786</v>
       </c>
       <c r="C122" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E122" s="12">
         <v>2.5000000000000001E-2</v>
@@ -2570,7 +2570,7 @@
         <v>39828</v>
       </c>
       <c r="C123" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E123" s="12">
         <v>0.02</v>
@@ -2590,7 +2590,7 @@
         <v>39849</v>
       </c>
       <c r="C124" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E124" s="12">
         <v>0.02</v>
@@ -2610,7 +2610,7 @@
         <v>39877</v>
       </c>
       <c r="C125" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E125" s="12">
         <v>1.4999999999999999E-2</v>
@@ -2630,7 +2630,7 @@
         <v>39905</v>
       </c>
       <c r="C126" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E126" s="12">
         <v>1.2500000000000001E-2</v>
@@ -2650,7 +2650,7 @@
         <v>39940</v>
       </c>
       <c r="C127" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E127" s="12">
         <v>0.01</v>
@@ -2670,7 +2670,7 @@
         <v>39968</v>
       </c>
       <c r="C128" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E128" s="12">
         <v>0.01</v>
@@ -2690,7 +2690,7 @@
         <v>39996</v>
       </c>
       <c r="C129" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E129" s="12">
         <v>0.01</v>
@@ -2710,7 +2710,7 @@
         <v>40031</v>
       </c>
       <c r="C130" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E130" s="12">
         <v>0.01</v>
@@ -2730,7 +2730,7 @@
         <v>40059</v>
       </c>
       <c r="C131" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E131" s="12">
         <v>0.01</v>
@@ -2750,7 +2750,7 @@
         <v>40094</v>
       </c>
       <c r="C132" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E132" s="12">
         <v>0.01</v>
@@ -2770,7 +2770,7 @@
         <v>40122</v>
       </c>
       <c r="C133" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E133" s="12">
         <v>0.01</v>
@@ -2790,7 +2790,7 @@
         <v>40150</v>
       </c>
       <c r="C134" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E134" s="12">
         <v>0.01</v>
@@ -2810,7 +2810,7 @@
         <v>40192</v>
       </c>
       <c r="C135" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E135" s="12">
         <v>0.01</v>
@@ -2830,7 +2830,7 @@
         <v>40213</v>
       </c>
       <c r="C136" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E136" s="12">
         <v>0.01</v>
@@ -2850,7 +2850,7 @@
         <v>40241</v>
       </c>
       <c r="C137" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E137" s="12">
         <v>0.01</v>
@@ -2870,7 +2870,7 @@
         <v>40276</v>
       </c>
       <c r="C138" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E138" s="12">
         <v>0.01</v>
@@ -2890,7 +2890,7 @@
         <v>40304</v>
       </c>
       <c r="C139" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E139" s="12">
         <v>0.01</v>
@@ -2910,7 +2910,7 @@
         <v>40339</v>
       </c>
       <c r="C140" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E140" s="12">
         <v>0.01</v>
@@ -2930,7 +2930,7 @@
         <v>40367</v>
       </c>
       <c r="C141" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E141" s="12">
         <v>0.01</v>
@@ -2950,7 +2950,7 @@
         <v>40395</v>
       </c>
       <c r="C142" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E142" s="12">
         <v>0.01</v>
@@ -2970,7 +2970,7 @@
         <v>40423</v>
       </c>
       <c r="C143" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E143" s="12">
         <v>0.01</v>
@@ -2990,7 +2990,7 @@
         <v>40458</v>
       </c>
       <c r="C144" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E144" s="12">
         <v>0.01</v>
@@ -3010,7 +3010,7 @@
         <v>40486</v>
       </c>
       <c r="C145" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E145" s="12">
         <v>0.01</v>
@@ -3030,7 +3030,7 @@
         <v>40514</v>
       </c>
       <c r="C146" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E146" s="12">
         <v>0.01</v>
@@ -3050,7 +3050,7 @@
         <v>40556</v>
       </c>
       <c r="C147" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E147" s="12">
         <v>0.01</v>
@@ -3070,7 +3070,7 @@
         <v>40577</v>
       </c>
       <c r="C148" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E148" s="12">
         <v>0.01</v>
@@ -3090,7 +3090,7 @@
         <v>40605</v>
       </c>
       <c r="C149" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E149" s="12">
         <v>0.01</v>
@@ -3110,7 +3110,7 @@
         <v>40640</v>
       </c>
       <c r="C150" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E150" s="12">
         <v>1.2500000000000001E-2</v>
@@ -3130,7 +3130,7 @@
         <v>40668</v>
       </c>
       <c r="C151" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E151" s="12">
         <v>1.2500000000000001E-2</v>
@@ -3150,7 +3150,7 @@
         <v>40703</v>
       </c>
       <c r="C152" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E152" s="12">
         <v>1.2500000000000001E-2</v>
@@ -3170,7 +3170,7 @@
         <v>40731</v>
       </c>
       <c r="C153" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E153" s="12">
         <v>1.4999999999999999E-2</v>
@@ -3190,7 +3190,7 @@
         <v>40759</v>
       </c>
       <c r="C154" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E154" s="12">
         <v>1.4999999999999999E-2</v>
@@ -3210,7 +3210,7 @@
         <v>40794</v>
       </c>
       <c r="C155" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E155" s="12">
         <v>1.4999999999999999E-2</v>
@@ -3230,7 +3230,7 @@
         <v>40822</v>
       </c>
       <c r="C156" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E156" s="12">
         <v>1.4999999999999999E-2</v>
@@ -3250,7 +3250,7 @@
         <v>40850</v>
       </c>
       <c r="C157" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E157" s="12">
         <v>1.2500000000000001E-2</v>
@@ -3270,7 +3270,7 @@
         <v>40885</v>
       </c>
       <c r="C158" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E158" s="12">
         <v>0.01</v>
@@ -3290,7 +3290,7 @@
         <v>40920</v>
       </c>
       <c r="C159" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E159" s="12">
         <v>0.01</v>
@@ -3310,7 +3310,7 @@
         <v>40948</v>
       </c>
       <c r="C160" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E160" s="12">
         <v>0.01</v>
@@ -3330,7 +3330,7 @@
         <v>40976</v>
       </c>
       <c r="C161" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E161" s="12">
         <v>0.01</v>
@@ -3350,7 +3350,7 @@
         <v>41003</v>
       </c>
       <c r="C162" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E162" s="12">
         <v>0.01</v>
@@ -3370,7 +3370,7 @@
         <v>41032</v>
       </c>
       <c r="C163" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E163" s="12">
         <v>0.01</v>
@@ -3390,7 +3390,7 @@
         <v>41066</v>
       </c>
       <c r="C164" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E164" s="12">
         <v>0.01</v>
@@ -3410,7 +3410,7 @@
         <v>41095</v>
       </c>
       <c r="C165" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E165" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3430,7 +3430,7 @@
         <v>41123</v>
       </c>
       <c r="C166" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E166" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3450,7 +3450,7 @@
         <v>41158</v>
       </c>
       <c r="C167" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E167" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3470,7 +3470,7 @@
         <v>41186</v>
       </c>
       <c r="C168" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E168" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3490,7 +3490,7 @@
         <v>41221</v>
       </c>
       <c r="C169" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E169" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3510,7 +3510,7 @@
         <v>41249</v>
       </c>
       <c r="C170" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E170" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3530,7 +3530,7 @@
         <v>41284</v>
       </c>
       <c r="C171" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E171" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3550,7 +3550,7 @@
         <v>41312</v>
       </c>
       <c r="C172" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E172" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3570,7 +3570,7 @@
         <v>41340</v>
       </c>
       <c r="C173" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E173" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3590,7 +3590,7 @@
         <v>41368</v>
       </c>
       <c r="C174" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E174" s="12">
         <v>7.4999999999999997E-3</v>
@@ -3610,7 +3610,7 @@
         <v>41396</v>
       </c>
       <c r="C175" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E175" s="12">
         <v>5.0000000000000001E-3</v>
@@ -3630,7 +3630,7 @@
         <v>41431</v>
       </c>
       <c r="C176" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E176" s="12">
         <v>5.0000000000000001E-3</v>
@@ -3650,7 +3650,7 @@
         <v>41459</v>
       </c>
       <c r="C177" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E177" s="12">
         <v>5.0000000000000001E-3</v>
@@ -3670,7 +3670,7 @@
         <v>41487</v>
       </c>
       <c r="C178" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E178" s="12">
         <v>5.0000000000000001E-3</v>
@@ -3690,7 +3690,7 @@
         <v>41522</v>
       </c>
       <c r="C179" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E179" s="12">
         <v>5.0000000000000001E-3</v>
@@ -3710,7 +3710,7 @@
         <v>41549</v>
       </c>
       <c r="C180" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E180" s="12">
         <v>5.0000000000000001E-3</v>
@@ -3730,7 +3730,7 @@
         <v>41585</v>
       </c>
       <c r="C181" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E181" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3750,7 +3750,7 @@
         <v>41613</v>
       </c>
       <c r="C182" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E182" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3770,7 +3770,7 @@
         <v>41648</v>
       </c>
       <c r="C183" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E183" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3790,7 +3790,7 @@
         <v>41676</v>
       </c>
       <c r="C184" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E184" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3810,7 +3810,7 @@
         <v>41704</v>
       </c>
       <c r="C185" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E185" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3830,7 +3830,7 @@
         <v>41732</v>
       </c>
       <c r="C186" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E186" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3850,7 +3850,7 @@
         <v>41767</v>
       </c>
       <c r="C187" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E187" s="12">
         <v>2.5000000000000001E-3</v>
@@ -3870,7 +3870,7 @@
         <v>41795</v>
       </c>
       <c r="C188" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E188" s="12">
         <v>1.5E-3</v>
@@ -3890,7 +3890,7 @@
         <v>41823</v>
       </c>
       <c r="C189" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E189" s="12">
         <v>1.5E-3</v>
@@ -3910,7 +3910,7 @@
         <v>41858</v>
       </c>
       <c r="C190" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E190" s="12">
         <v>1.5E-3</v>
@@ -3930,7 +3930,7 @@
         <v>41886</v>
       </c>
       <c r="C191" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E191" s="12">
         <v>5.0000000000000001E-4</v>
@@ -3950,7 +3950,7 @@
         <v>41914</v>
       </c>
       <c r="C192" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E192" s="12">
         <v>5.0000000000000001E-4</v>
@@ -3970,7 +3970,7 @@
         <v>41949</v>
       </c>
       <c r="C193" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E193" s="12">
         <v>5.0000000000000001E-4</v>
@@ -3990,7 +3990,7 @@
         <v>41977</v>
       </c>
       <c r="C194" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E194" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4010,7 +4010,7 @@
         <v>42026</v>
       </c>
       <c r="C195" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E195" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4030,7 +4030,7 @@
         <v>42068</v>
       </c>
       <c r="C196" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E196" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4050,7 +4050,7 @@
         <v>42109</v>
       </c>
       <c r="C197" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E197" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4070,7 +4070,7 @@
         <v>42158</v>
       </c>
       <c r="C198" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E198" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4090,7 +4090,7 @@
         <v>42201</v>
       </c>
       <c r="C199" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E199" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4110,7 +4110,7 @@
         <v>42250</v>
       </c>
       <c r="C200" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E200" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4130,7 +4130,7 @@
         <v>42299</v>
       </c>
       <c r="C201" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E201" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4150,7 +4150,7 @@
         <v>42341</v>
       </c>
       <c r="C202" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E202" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4170,7 +4170,7 @@
         <v>42390</v>
       </c>
       <c r="C203" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E203" s="12">
         <v>5.0000000000000001E-4</v>
@@ -4190,7 +4190,7 @@
         <v>42439</v>
       </c>
       <c r="C204" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E204" s="12">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>42481</v>
       </c>
       <c r="C205" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E205" s="12">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>42523</v>
       </c>
       <c r="C206" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E206" s="12">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>42572</v>
       </c>
       <c r="C207" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E207" s="12">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         <v>42621</v>
       </c>
       <c r="C208" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E208" s="12">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>42663</v>
       </c>
       <c r="C209" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E209" s="12">
         <v>0</v>
@@ -4310,7 +4310,7 @@
         <v>42712</v>
       </c>
       <c r="C210" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E210" s="12">
         <v>0</v>
@@ -4330,7 +4330,7 @@
         <v>42754</v>
       </c>
       <c r="C211" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E211" s="12">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>42803</v>
       </c>
       <c r="C212" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E212" s="12">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>42852</v>
       </c>
       <c r="C213" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E213" s="12">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>42894</v>
       </c>
       <c r="C214" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E214" s="12">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         <v>42936</v>
       </c>
       <c r="C215" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E215" s="12">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>42985</v>
       </c>
       <c r="C216" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E216" s="12">
         <v>0</v>
@@ -4450,7 +4450,7 @@
         <v>43034</v>
       </c>
       <c r="C217" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E217" s="12">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         <v>43083</v>
       </c>
       <c r="C218" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E218" s="12">
         <v>0</v>
@@ -4490,7 +4490,7 @@
         <v>43125</v>
       </c>
       <c r="C219" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E219" s="12">
         <v>0</v>
@@ -4510,7 +4510,7 @@
         <v>43167</v>
       </c>
       <c r="C220" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E220" s="12">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>43216</v>
       </c>
       <c r="C221" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E221" s="12">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>43265</v>
       </c>
       <c r="C222" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E222" s="12">
         <v>0</v>
@@ -4570,7 +4570,7 @@
         <v>43307</v>
       </c>
       <c r="C223" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E223" s="12">
         <v>0</v>
@@ -4590,7 +4590,7 @@
         <v>43356</v>
       </c>
       <c r="C224" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E224" s="12">
         <v>0</v>
@@ -4610,7 +4610,7 @@
         <v>43398</v>
       </c>
       <c r="C225" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E225" s="12">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>43447</v>
       </c>
       <c r="C226" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E226" s="12">
         <v>0</v>
@@ -4650,7 +4650,7 @@
         <v>43489</v>
       </c>
       <c r="C227" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E227" s="12">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>43531</v>
       </c>
       <c r="C228" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E228" s="12">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>43565</v>
       </c>
       <c r="C229" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E229" s="12">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         <v>43622</v>
       </c>
       <c r="C230" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E230" s="12">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         <v>43671</v>
       </c>
       <c r="C231" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E231" s="12">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         <v>43720</v>
       </c>
       <c r="C232" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E232" s="12">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         <v>43762</v>
       </c>
       <c r="C233" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E233" s="12">
         <v>0</v>
@@ -4790,7 +4790,7 @@
         <v>43811</v>
       </c>
       <c r="C234" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E234" s="12">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>43853</v>
       </c>
       <c r="C235" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E235" s="12">
         <v>0</v>
@@ -4830,7 +4830,7 @@
         <v>43902</v>
       </c>
       <c r="C236" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E236" s="12">
         <v>0</v>
@@ -4850,7 +4850,7 @@
         <v>43951</v>
       </c>
       <c r="C237" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E237" s="12">
         <v>0</v>
@@ -4870,7 +4870,7 @@
         <v>43986</v>
       </c>
       <c r="C238" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E238" s="12">
         <v>0</v>
@@ -4890,7 +4890,7 @@
         <v>44028</v>
       </c>
       <c r="C239" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E239" s="12">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         <v>44084</v>
       </c>
       <c r="C240" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E240" s="12">
         <v>0</v>
@@ -4930,7 +4930,7 @@
         <v>44133</v>
       </c>
       <c r="C241" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E241" s="12">
         <v>0</v>
@@ -4950,7 +4950,7 @@
         <v>44175</v>
       </c>
       <c r="C242" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E242" s="12">
         <v>0</v>
@@ -4970,7 +4970,7 @@
         <v>44217</v>
       </c>
       <c r="C243" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E243" s="12">
         <v>0</v>
@@ -4990,7 +4990,7 @@
         <v>44266</v>
       </c>
       <c r="C244" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E244" s="12">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>44308</v>
       </c>
       <c r="C245" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E245" s="12">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>44357</v>
       </c>
       <c r="C246" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E246" s="12">
         <v>0</v>
@@ -5050,7 +5050,7 @@
         <v>44399</v>
       </c>
       <c r="C247" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E247" s="12">
         <v>0</v>
@@ -5070,7 +5070,7 @@
         <v>44448</v>
       </c>
       <c r="C248" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E248" s="12">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>44497</v>
       </c>
       <c r="C249" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E249" s="12">
         <v>0</v>
@@ -5110,7 +5110,7 @@
         <v>44546</v>
       </c>
       <c r="C250" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E250" s="12">
         <v>0</v>
@@ -5130,7 +5130,7 @@
         <v>44595</v>
       </c>
       <c r="C251" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E251" s="12">
         <v>0</v>
@@ -5150,7 +5150,7 @@
         <v>44630</v>
       </c>
       <c r="C252" s="9">
-        <v>0.32291666666666669</v>
+        <v>0.34375</v>
       </c>
       <c r="E252" s="12">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         <v>44665</v>
       </c>
       <c r="C253" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E253" s="12">
         <v>0</v>
@@ -5190,7 +5190,7 @@
         <v>44721</v>
       </c>
       <c r="C254" s="9">
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="E254" s="12">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         <v>44763</v>
       </c>
       <c r="C255" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E255" s="12">
         <v>5.0000000000000001E-3</v>
@@ -5230,7 +5230,7 @@
         <v>44812</v>
       </c>
       <c r="C256" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E256" s="12">
         <v>1.2500000000000001E-2</v>
@@ -5250,7 +5250,7 @@
         <v>44861</v>
       </c>
       <c r="C257" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E257" s="12">
         <v>0.02</v>
@@ -5330,7 +5330,7 @@
         <v>45050</v>
       </c>
       <c r="C261" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E261" s="12">
         <v>3.7499999999999999E-2</v>
@@ -5350,7 +5350,7 @@
         <v>45092</v>
       </c>
       <c r="C262" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E262" s="12">
         <v>0.04</v>
@@ -5370,7 +5370,7 @@
         <v>45134</v>
       </c>
       <c r="C263" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E263" s="12">
         <v>4.2500000000000003E-2</v>
@@ -5390,7 +5390,7 @@
         <v>45183</v>
       </c>
       <c r="C264" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E264" s="12">
         <v>4.4999999999999998E-2</v>
@@ -5410,7 +5410,7 @@
         <v>45225</v>
       </c>
       <c r="C265" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E265" s="12">
         <v>4.4999999999999998E-2</v>
@@ -5490,7 +5490,7 @@
         <v>45393</v>
       </c>
       <c r="C269" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E269" s="12">
         <v>4.4999999999999998E-2</v>
@@ -5510,7 +5510,7 @@
         <v>45449</v>
       </c>
       <c r="C270" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E270" s="12">
         <v>4.2500000000000003E-2</v>
@@ -5530,7 +5530,7 @@
         <v>45491</v>
       </c>
       <c r="C271" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E271" s="12">
         <v>4.2500000000000003E-2</v>
@@ -5550,7 +5550,7 @@
         <v>45547</v>
       </c>
       <c r="C272" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E272" s="12">
         <v>3.6499999999999998E-2</v>
@@ -5570,7 +5570,7 @@
         <v>45582</v>
       </c>
       <c r="C273" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E273" s="12">
         <v>3.4000000000000002E-2</v>
@@ -5650,7 +5650,7 @@
         <v>45764</v>
       </c>
       <c r="C277" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E277" s="12">
         <v>2.4E-2</v>
@@ -5670,7 +5670,7 @@
         <v>45813</v>
       </c>
       <c r="C278" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E278" s="12">
         <v>2.1499999999999998E-2</v>
@@ -5690,7 +5690,7 @@
         <v>45862</v>
       </c>
       <c r="C279" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E279" s="12">
         <v>2.1499999999999998E-2</v>
@@ -5710,7 +5710,7 @@
         <v>45911</v>
       </c>
       <c r="C280" s="9">
-        <v>0.30208333333333331</v>
+        <v>0.34375</v>
       </c>
       <c r="E280" s="12">
         <v>2.1499999999999998E-2</v>
@@ -5799,6 +5799,26 @@
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="G284" s="12">
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="10">
+        <v>46142</v>
+      </c>
+      <c r="B285" s="6">
+        <v>46142</v>
+      </c>
+      <c r="C285" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="E285" s="12">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="F285" s="12">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="G285" s="12">
         <v>2.1499999999999998E-2</v>
       </c>
     </row>
@@ -5811,10 +5831,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B93410-546A-419A-A73F-C6043DD8CD5B}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="10.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
